--- a/data/trans_dic/IP07_C15_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Provincia-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 19,62</t>
+          <t>4,32; 26,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 26,03</t>
+          <t>6,19; 25,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 18,26</t>
+          <t>7,77; 21,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 42,96</t>
+          <t>20,84; 55,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,83; 56,99</t>
+          <t>10,42; 43,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,66; 45,67</t>
+          <t>21,62; 45,13</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,53</t>
+          <t>0,0; 17,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 75,93</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 18,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 42,66</t>
+          <t>13,71; 57,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,68; 59,01</t>
+          <t>8,86; 43,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,39; 43,74</t>
+          <t>16,17; 44,09</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,53; 46,87</t>
+          <t>8,07; 34,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 34,51</t>
+          <t>14,36; 48,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,79; 34,65</t>
+          <t>13,95; 34,08</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,25</t>
+          <t>7,5; 15,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,06</t>
+          <t>8,34; 16,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,19</t>
+          <t>8,61; 13,98</t>
         </is>
       </c>
     </row>
@@ -1029,18 +1029,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11094</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>826; 11977</t>
+          <t>2033; 12516</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2032; 13098</t>
+          <t>2328; 9467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4517; 20337</t>
+          <t>6580; 18463</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>12763</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1903; 7909</t>
+          <t>4545; 12132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5498; 13721</t>
+          <t>1914; 8080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9204; 19403</t>
+          <t>8688; 18135</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>492</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1895</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 2231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3351</t>
+          <t>0; 3696</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>490</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2444</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2746</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2535</t>
+          <t>0; 2538</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>8892</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1296; 6945</t>
+          <t>2234; 9314</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2759; 10383</t>
+          <t>1509; 7404</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5215; 14818</t>
+          <t>5389; 14694</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13948</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3079; 10663</t>
+          <t>3087; 13360</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2713; 12887</t>
+          <t>3456; 11611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8284; 20823</t>
+          <t>8692; 21244</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1604</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1867</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2277</t>
+          <t>0; 2075</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11854; 30319</t>
+          <t>18627; 37449</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19212; 40210</t>
+          <t>15458; 30076</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36702; 63756</t>
+          <t>37331; 60644</t>
         </is>
       </c>
     </row>
